--- a/program/tab3.xlsx
+++ b/program/tab3.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="4">
   <si>
     <t>w1</t>
   </si>
@@ -452,13 +452,13 @@
         <v>2.5</v>
       </c>
       <c r="B2" s="5">
-        <v>265967.34772368631</v>
+        <v>265291.05477820878</v>
       </c>
       <c r="C2" s="5">
-        <v>431.59795252960487</v>
+        <v>428.91108665444909</v>
       </c>
       <c r="D2" s="5">
-        <v>18650.921991806797</v>
+        <v>18646.819907509853</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
@@ -466,13 +466,13 @@
         <v>3</v>
       </c>
       <c r="B3" s="5">
-        <v>319160.81726842356</v>
+        <v>318349.26573385048</v>
       </c>
       <c r="C3" s="5">
-        <v>499.37221268631208</v>
+        <v>496.26342556300932</v>
       </c>
       <c r="D3" s="5">
-        <v>21579.695012685435</v>
+        <v>21574.948773969554</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
@@ -480,13 +480,13 @@
         <v>3.5</v>
       </c>
       <c r="B4" s="5">
-        <v>372354.28681316081</v>
+        <v>371407.47668949224</v>
       </c>
       <c r="C4" s="5">
-        <v>564.9133060548761</v>
+        <v>561.39650001915652</v>
       </c>
       <c r="D4" s="5">
-        <v>24411.964750088708</v>
+        <v>24406.595581888712</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
@@ -494,13 +494,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>425547.75635789812</v>
+        <v>424465.68764513405</v>
       </c>
       <c r="C5" s="5">
-        <v>628.60142597979848</v>
+        <v>624.68813651528581</v>
       </c>
       <c r="D5" s="5">
-        <v>27164.160745372268</v>
+        <v>27158.186259109225</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
@@ -508,13 +508,13 @@
         <v>4.5</v>
       </c>
       <c r="B6" s="5">
-        <v>478741.22590263537</v>
+        <v>477523.89860077581</v>
       </c>
       <c r="C6" s="5">
-        <v>690.71260213827657</v>
+        <v>686.41264633601156</v>
       </c>
       <c r="D6" s="5">
-        <v>29848.211247840034</v>
+        <v>29841.646431435493</v>
       </c>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
@@ -522,13 +522,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="5">
-        <v>531934.69544737262</v>
+        <v>530582.10955641756</v>
       </c>
       <c r="C7" s="5">
-        <v>751.45568138420276</v>
+        <v>746.77757618196665</v>
       </c>
       <c r="D7" s="5">
-        <v>32473.141291918957</v>
+        <v>32465.999148328166</v>
       </c>
     </row>
   </sheetData>

--- a/program/tab3.xlsx
+++ b/program/tab3.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PAROGENA\program\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Palych\Desktop\PAROGENA\program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02B8AA9-7EAD-4E79-A179-4E2179C8FD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8734CED-2BAF-4451-BA0D-DDAFE2B5D251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9375" yWindow="1785" windowWidth="28800" windowHeight="11295"/>
+    <workbookView xWindow="0" yWindow="2055" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>w1</t>
   </si>
@@ -37,8 +42,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -59,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -67,29 +75,30 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -108,7 +117,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
@@ -259,7 +268,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -283,9 +292,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -309,7 +318,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -344,7 +353,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -362,7 +371,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -387,7 +396,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -423,115 +432,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="4" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="7.140625" style="2" bestFit="true" customWidth="true"/>
-    <col min="3" max="3" width="4.7109375" style="2" bestFit="true" customWidth="true"/>
-    <col min="4" max="4" width="7" style="2" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>2.5</v>
       </c>
-      <c r="B2" s="5">
-        <v>265291.05477820878</v>
-      </c>
-      <c r="C2" s="5">
-        <v>428.91108665444909</v>
-      </c>
-      <c r="D2" s="5">
-        <v>18646.819907509853</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="B2" s="3">
+        <v>265967.34772368631</v>
+      </c>
+      <c r="C2" s="3">
+        <v>431.59795252960487</v>
+      </c>
+      <c r="D2" s="3">
+        <v>18650.921991806797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>3</v>
       </c>
-      <c r="B3" s="5">
-        <v>318349.26573385048</v>
-      </c>
-      <c r="C3" s="5">
-        <v>496.26342556300932</v>
-      </c>
-      <c r="D3" s="5">
-        <v>21574.948773969554</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="B3" s="3">
+        <v>319160.81726842356</v>
+      </c>
+      <c r="C3" s="3">
+        <v>499.37221268631208</v>
+      </c>
+      <c r="D3" s="3">
+        <v>21579.695012685435</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>3.5</v>
       </c>
-      <c r="B4" s="5">
-        <v>371407.47668949224</v>
-      </c>
-      <c r="C4" s="5">
-        <v>561.39650001915652</v>
-      </c>
-      <c r="D4" s="5">
-        <v>24406.595581888712</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="B4" s="3">
+        <v>372354.28681316081</v>
+      </c>
+      <c r="C4" s="3">
+        <v>564.9133060548761</v>
+      </c>
+      <c r="D4" s="3">
+        <v>24411.964750088708</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
-        <v>424465.68764513405</v>
-      </c>
-      <c r="C5" s="5">
-        <v>624.68813651528581</v>
-      </c>
-      <c r="D5" s="5">
-        <v>27158.186259109225</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="B5" s="3">
+        <v>425547.75635789812</v>
+      </c>
+      <c r="C5" s="3">
+        <v>628.60142597979848</v>
+      </c>
+      <c r="D5" s="3">
+        <v>27164.160745372268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>4.5</v>
       </c>
-      <c r="B6" s="5">
-        <v>477523.89860077581</v>
-      </c>
-      <c r="C6" s="5">
-        <v>686.41264633601156</v>
-      </c>
-      <c r="D6" s="5">
-        <v>29841.646431435493</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="B6" s="3">
+        <v>478741.22590263537</v>
+      </c>
+      <c r="C6" s="3">
+        <v>690.71260213827657</v>
+      </c>
+      <c r="D6" s="3">
+        <v>29848.211247840034</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>530582.10955641756</v>
-      </c>
-      <c r="C7" s="5">
-        <v>746.77757618196665</v>
-      </c>
-      <c r="D7" s="5">
-        <v>32465.999148328166</v>
+      <c r="B7" s="3">
+        <v>531934.69544737262</v>
+      </c>
+      <c r="C7" s="3">
+        <v>751.45568138420276</v>
+      </c>
+      <c r="D7" s="3">
+        <v>32473.141291918957</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/program/tab3.xlsx
+++ b/program/tab3.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8734CED-2BAF-4451-BA0D-DDAFE2B5D251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2055" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2055" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8" uniqueCount="4">
   <si>
     <t>w1</t>
   </si>
@@ -42,11 +42,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -67,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,30 +75,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -117,7 +119,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
@@ -268,7 +270,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -292,9 +294,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -318,7 +320,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -353,7 +355,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -371,7 +373,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -396,7 +398,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -432,17 +434,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="5" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="7.140625" style="2" bestFit="true" customWidth="true"/>
+    <col min="3" max="3" width="4.7109375" style="3" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="7" style="2" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -456,7 +458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2.5</v>
       </c>
@@ -470,7 +472,7 @@
         <v>18650.921991806797</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -484,7 +486,7 @@
         <v>21579.695012685435</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3.5</v>
       </c>
@@ -498,7 +500,7 @@
         <v>24411.964750088708</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -512,7 +514,7 @@
         <v>27164.160745372268</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>4.5</v>
       </c>
@@ -526,7 +528,7 @@
         <v>29848.211247840034</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>5</v>
       </c>

--- a/program/tab3.xlsx
+++ b/program/tab3.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="4">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab3.xlsx
+++ b/program/tab3.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16" uniqueCount="4">
   <si>
     <t>w1</t>
   </si>

--- a/program/tab3.xlsx
+++ b/program/tab3.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="4">
   <si>
     <t>w1</t>
   </si>
